--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536137_LIGAREGULARA_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536137_LIGAREGULARA_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y30"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,7 +546,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. TAMAYO LESMES</t>
+          <t>D. LOPEZ RIANO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -558,67 +558,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5158</v>
+        <v>5.5735</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8124</v>
+        <v>3.3976</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7034</v>
+        <v>2.1758</v>
       </c>
       <c r="G2" t="n">
-        <v>3.94</v>
+        <v>5.1697</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7204</v>
+        <v>5.3139</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2196</v>
+        <v>-0.1441</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1907</v>
+        <v>4.4124</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2466</v>
+        <v>4.4369</v>
       </c>
       <c r="L2" t="n">
-        <v>1.9441</v>
+        <v>-0.0245</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7493</v>
+        <v>0.7573</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4738</v>
+        <v>0.8769</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2755</v>
+        <v>-0.1196</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9749</v>
+        <v>1.9499</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9749</v>
+        <v>1.9499</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0092</v>
+        <v>0.3369</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2669</v>
+        <v>-0.3519</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2577</v>
+        <v>0.6887</v>
       </c>
       <c r="V2" t="n">
-        <v>0.61</v>
+        <v>-1.883</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8885999999999999</v>
+        <v>-0.6629</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2786</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. LOPEZ RIANO</t>
+          <t>A. TAMAYO LESMES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -641,67 +641,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2659</v>
+        <v>5.5158</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0901</v>
+        <v>3.8124</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1758</v>
+        <v>1.7034</v>
       </c>
       <c r="G3" t="n">
-        <v>4.8622</v>
+        <v>3.94</v>
       </c>
       <c r="H3" t="n">
-        <v>5.0063</v>
+        <v>1.7204</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1441</v>
+        <v>2.2196</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1049</v>
+        <v>3.1907</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1294</v>
+        <v>1.2466</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0245</v>
+        <v>1.9441</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7573</v>
+        <v>0.7493</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8769</v>
+        <v>0.4738</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1196</v>
+        <v>0.2755</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9499</v>
+        <v>0.9749</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9499</v>
+        <v>0.9749</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3369</v>
+        <v>-0.0092</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3519</v>
+        <v>-0.2669</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6887</v>
+        <v>0.2577</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.883</v>
+        <v>0.61</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.6629</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2201</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. GONZÁLEZ RAMÍREZ</t>
+          <t>J. SANTANO BARTOLOME</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1222,67 +1222,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.615</v>
+        <v>0.2391</v>
       </c>
       <c r="E10" t="n">
-        <v>0.615</v>
+        <v>-2.2821</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>2.5212</v>
       </c>
       <c r="G10" t="n">
-        <v>0.615</v>
+        <v>3.0327</v>
       </c>
       <c r="H10" t="n">
-        <v>0.615</v>
+        <v>1.6458</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1.3869</v>
       </c>
       <c r="J10" t="n">
-        <v>0.615</v>
+        <v>1.6687</v>
       </c>
       <c r="K10" t="n">
-        <v>0.615</v>
+        <v>0.9722</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.6965</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.364</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>0.6736</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.6904</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-1.9499</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-3.8997</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.9499</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.0977</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>-0.3296</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.4274</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.9415</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2786</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. LOPEZ RIAÑO</t>
+          <t>B. GONZALEZ RAMIREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1305,58 +1305,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3075</v>
+        <v>-0.1728</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3075</v>
+        <v>-1.403</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1.2302</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3075</v>
+        <v>-1.1945</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3075</v>
+        <v>1.4983</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-2.6929</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3075</v>
+        <v>-0.1103</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3075</v>
+        <v>1.9152</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-2.0255</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>-1.0843</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-0.4169</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0.6673</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.3649</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.6318</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>-0.3178</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.9496</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1376,7 +1376,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. SANTANO BARTOLOME</t>
+          <t>W. TSAFACK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1388,64 +1388,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2391</v>
+        <v>-3.7067</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2821</v>
+        <v>-2.7666</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5212</v>
+        <v>-0.9401</v>
       </c>
       <c r="G12" t="n">
-        <v>3.0327</v>
+        <v>-3.4082</v>
       </c>
       <c r="H12" t="n">
-        <v>1.6458</v>
+        <v>-3.533</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3869</v>
+        <v>0.1248</v>
       </c>
       <c r="J12" t="n">
-        <v>1.6687</v>
+        <v>-2.588</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9722</v>
+        <v>-2.7095</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6965</v>
+        <v>0.1215</v>
       </c>
       <c r="M12" t="n">
-        <v>1.364</v>
+        <v>-0.8202</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6736</v>
+        <v>-0.8235</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6904</v>
+        <v>0.0033</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.9499</v>
+        <v>0.7799</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.8997</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.9499</v>
+        <v>0.7799</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0977</v>
+        <v>0.8045</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3296</v>
+        <v>0.4843</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4274</v>
+        <v>0.3202</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9415</v>
+        <v>-1.883</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2786</v>
+        <v>-0.6629</v>
       </c>
       <c r="X12" t="n">
         <v>-1.2201</v>
@@ -1459,7 +1459,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B. GONZALEZ RAMIREZ</t>
+          <t>G. PEREZ RAMIREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1471,67 +1471,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-3.82</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.0181</v>
+        <v>-4.1032</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2302</v>
+        <v>0.2832</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.8096</v>
+        <v>-1.8372</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8833</v>
+        <v>0.7648</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.6929</v>
+        <v>-2.602</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7252999999999999</v>
+        <v>-1.8485</v>
       </c>
       <c r="K13" t="n">
-        <v>1.3002</v>
+        <v>0.2255</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.0255</v>
+        <v>-2.074</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.0843</v>
+        <v>0.0113</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4169</v>
+        <v>0.5393</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6673</v>
+        <v>-0.5279</v>
       </c>
       <c r="P13" t="n">
-        <v>0.39</v>
+        <v>-0.7799</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9749</v>
+        <v>-1.9499</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3649</v>
+        <v>1.1699</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6318</v>
+        <v>-0.0357</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3178</v>
+        <v>-0.3048</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9496</v>
+        <v>0.2691</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-1.1671</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.1671</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>W. TSAFACK</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1554,150 +1554,146 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.7067</v>
+        <v>10.0253</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.7666</v>
+        <v>-5.582599999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9401</v>
+        <v>15.6079</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.4082</v>
+        <v>4.1089</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.533</v>
+        <v>4.109</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1248</v>
+        <v>-8.881784197001252e-16</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.588</v>
+        <v>4.070999999999998</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.7095</v>
+        <v>3.5059</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1215</v>
+        <v>0.5652000000000008</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8202</v>
+        <v>0.03790000000000018</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8235</v>
+        <v>0.6032</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0033</v>
+        <v>-0.5650000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7799</v>
+        <v>3.899700000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-11.6992</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7799</v>
+        <v>15.5988</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8045</v>
+        <v>3.899700000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4843</v>
+        <v>-1.0715</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3202</v>
+        <v>4.9712</v>
       </c>
       <c r="V14" t="n">
         <v>-1.883</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6629</v>
+        <v>3.1173</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2201</v>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>play_by_play_2536137_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
+        <v>-5.0001</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. PEREZ RAMIREZ</t>
+          <t>J. SCHILB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SPANISH BASKETBALL ACADEMY</t>
+          <t>MOVISTAR ESTUDIANTES</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.82</v>
+        <v>1.5501</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.1032</v>
+        <v>1.3828</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2832</v>
+        <v>0.1673</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.8372</v>
+        <v>1.5199</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7648</v>
+        <v>-1.0416</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.602</v>
+        <v>2.5615</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.8485</v>
+        <v>2.8732</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2255</v>
+        <v>-0.8935</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.074</v>
+        <v>3.7666</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0113</v>
+        <v>-1.3533</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5393</v>
+        <v>-0.1481</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5279</v>
+        <v>-1.2052</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7799</v>
+        <v>-0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9499</v>
+        <v>-0.9749</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1699</v>
+        <v>0.9749</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0357</v>
+        <v>-0.6327</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3048</v>
+        <v>-0.5155</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2691</v>
+        <v>-0.1173</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.1671</v>
+        <v>0.6629</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1671</v>
+        <v>0.6629</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1708,86 +1704,90 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>G. PEREZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SPANISH BASKETBALL ACADEMY</t>
+          <t>MOVISTAR ESTUDIANTES</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>10.0252</v>
+        <v>1.5103</v>
       </c>
       <c r="E16" t="n">
-        <v>-5.582699999999998</v>
+        <v>1.3058</v>
       </c>
       <c r="F16" t="n">
-        <v>15.6079</v>
+        <v>0.2045</v>
       </c>
       <c r="G16" t="n">
-        <v>4.108799999999999</v>
+        <v>0.7207</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1089</v>
+        <v>0.0336</v>
       </c>
       <c r="I16" t="n">
-        <v>-8.881784197001252e-16</v>
+        <v>0.6871</v>
       </c>
       <c r="J16" t="n">
-        <v>4.071</v>
+        <v>0.5111</v>
       </c>
       <c r="K16" t="n">
-        <v>3.5059</v>
+        <v>-0.2989</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5652000000000008</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>0.03790000000000018</v>
+        <v>0.2096</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6032</v>
+        <v>0.3325</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5650000000000001</v>
+        <v>-0.1229</v>
       </c>
       <c r="P16" t="n">
-        <v>3.899700000000001</v>
+        <v>0.7799</v>
       </c>
       <c r="Q16" t="n">
-        <v>-11.6992</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>15.5988</v>
+        <v>0.7799</v>
       </c>
       <c r="S16" t="n">
-        <v>3.899700000000001</v>
+        <v>-0.6004</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0715</v>
+        <v>-0.7039</v>
       </c>
       <c r="U16" t="n">
-        <v>4.9712</v>
+        <v>0.1035</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.883</v>
+        <v>0.61</v>
       </c>
       <c r="W16" t="n">
-        <v>3.1173</v>
+        <v>1.4986</v>
       </c>
       <c r="X16" t="n">
-        <v>-5.0001</v>
-      </c>
-      <c r="Y16" t="inlineStr"/>
+        <v>-0.8885999999999999</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2536137_LIGAREGULARA_PROCESSED.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. SCHILB</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1799,67 +1799,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5501</v>
+        <v>1.0904</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3828</v>
+        <v>0.8154</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1673</v>
+        <v>0.275</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5199</v>
+        <v>0.7093</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0416</v>
+        <v>-1.5865</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5615</v>
+        <v>2.2959</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8732</v>
+        <v>0.6441</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.8935</v>
+        <v>-0.6924</v>
       </c>
       <c r="L17" t="n">
-        <v>3.7666</v>
+        <v>1.3365</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3533</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1481</v>
+        <v>-0.8941</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2052</v>
+        <v>0.9593</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>1.3649</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9749</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9749</v>
+        <v>1.3649</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6327</v>
+        <v>0.2362</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5155</v>
+        <v>-0.3859</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1173</v>
+        <v>0.6221</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6629</v>
+        <v>-1.2201</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.5571</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6629</v>
+        <v>-1.7772</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. PEREZ HERNANDEZ</t>
+          <t>D. DAMIAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,67 +1882,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5103</v>
+        <v>0.8481</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3058</v>
+        <v>-1.3015</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2045</v>
+        <v>2.1496</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7207</v>
+        <v>2.5105</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0336</v>
+        <v>2.3565</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6871</v>
+        <v>0.154</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5111</v>
+        <v>2.2387</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2989</v>
+        <v>2.2307</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.008</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2096</v>
+        <v>0.2718</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3325</v>
+        <v>0.1258</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1229</v>
+        <v>0.146</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7799</v>
+        <v>-1.9499</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.1198</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7799</v>
+        <v>1.1699</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6004</v>
+        <v>0.619</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7039</v>
+        <v>-0.3675</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1035</v>
+        <v>0.9865</v>
       </c>
       <c r="V18" t="n">
-        <v>0.61</v>
+        <v>-0.3315</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4986</v>
+        <v>-0.0529</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8885999999999999</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>A. REDONDO ALVAREZ DE SOTOMAYOR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0904</v>
+        <v>0.5251</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8154</v>
+        <v>0.699</v>
       </c>
       <c r="F19" t="n">
-        <v>0.275</v>
+        <v>-0.1739</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7093</v>
+        <v>0.7532</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5865</v>
+        <v>0.3303</v>
       </c>
       <c r="I19" t="n">
-        <v>2.2959</v>
+        <v>0.4229</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6441</v>
+        <v>1.3651</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6924</v>
+        <v>0.6765</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3365</v>
+        <v>0.6885</v>
       </c>
       <c r="M19" t="n">
-        <v>0.06519999999999999</v>
+        <v>-0.6119</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8941</v>
+        <v>-0.3463</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9593</v>
+        <v>-0.2656</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3649</v>
+        <v>0.585</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.195</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3649</v>
+        <v>0.7799</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2362</v>
+        <v>-0.8129999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3859</v>
+        <v>-0.4711</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6221</v>
+        <v>-0.3419</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2201</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5571</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.7772</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. DAMIAN</t>
+          <t>F. ESPINOSA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,67 +2048,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8481</v>
+        <v>0.3884</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3015</v>
+        <v>-0.0294</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1496</v>
+        <v>0.4178</v>
       </c>
       <c r="G20" t="n">
-        <v>2.5105</v>
+        <v>0.0655</v>
       </c>
       <c r="H20" t="n">
-        <v>2.3565</v>
+        <v>1.07</v>
       </c>
       <c r="I20" t="n">
-        <v>0.154</v>
+        <v>-1.0045</v>
       </c>
       <c r="J20" t="n">
-        <v>2.2387</v>
+        <v>0.3396</v>
       </c>
       <c r="K20" t="n">
-        <v>2.2307</v>
+        <v>1.6196</v>
       </c>
       <c r="L20" t="n">
-        <v>0.008</v>
+        <v>-1.28</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2718</v>
+        <v>-0.2741</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1258</v>
+        <v>-0.5496</v>
       </c>
       <c r="O20" t="n">
-        <v>0.146</v>
+        <v>0.2755</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.9499</v>
+        <v>0.39</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.1198</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1699</v>
+        <v>0.39</v>
       </c>
       <c r="S20" t="n">
-        <v>0.619</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3675</v>
+        <v>-0.369</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9865</v>
+        <v>0.3019</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3315</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.0529</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2786</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. REDONDO ALVAREZ DE SOTOMAYOR</t>
+          <t>G. DE BONROSTRO GALLEGO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,58 +2131,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5251</v>
+        <v>0.1766</v>
       </c>
       <c r="E21" t="n">
-        <v>0.699</v>
+        <v>-0.0184</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1739</v>
+        <v>0.195</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7532</v>
+        <v>0.0405</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3303</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4229</v>
+        <v>0.0405</v>
       </c>
       <c r="J21" t="n">
-        <v>1.3651</v>
+        <v>0.0405</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6765</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6885</v>
+        <v>0.0405</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6119</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3463</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2656</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.585</v>
+        <v>0.195</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.195</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7799</v>
+        <v>0.195</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8129999999999999</v>
+        <v>-0.0589</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4711</v>
+        <v>-0.0589</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3419</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. ESPINOSA</t>
+          <t>H. APARICIO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,58 +2214,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3884</v>
+        <v>-0.8191000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0294</v>
+        <v>-0.8385</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4178</v>
+        <v>0.0194</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0655</v>
+        <v>-0.1266</v>
       </c>
       <c r="H22" t="n">
-        <v>1.07</v>
+        <v>-2.0951</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0045</v>
+        <v>1.9686</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3396</v>
+        <v>0.4871</v>
       </c>
       <c r="K22" t="n">
-        <v>1.6196</v>
+        <v>-0.9305</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.28</v>
+        <v>1.4176</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2741</v>
+        <v>-0.6136</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5496</v>
+        <v>-1.1646</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2755</v>
+        <v>0.551</v>
       </c>
       <c r="P22" t="n">
-        <v>0.39</v>
+        <v>-0.195</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R22" t="n">
-        <v>0.39</v>
+        <v>0.7799</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.06710000000000001</v>
+        <v>-0.4976</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.369</v>
+        <v>-0.3506</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3019</v>
+        <v>-0.147</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>H. APARICIO RODRÍGUEZ</t>
+          <t>S. GRADIN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,67 +2297,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3075</v>
+        <v>-1.2701</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3075</v>
+        <v>-2.1469</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.8768</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3075</v>
+        <v>-1.5962</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3075</v>
+        <v>0.6526</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>-2.2488</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3075</v>
+        <v>-1.2629</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3075</v>
+        <v>0.0496</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-1.3125</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>-0.3333</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>0.603</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>-0.9363</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-0.7799</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.9499</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.1699</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.0531</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>-0.1542</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.2073</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.0529</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.2201</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.1671</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>G. DE BONROSTRO GALLEGO</t>
+          <t>P. ROBLES LLANOS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2380,64 +2380,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1766</v>
+        <v>-2.8792</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0184</v>
+        <v>-5.5492</v>
       </c>
       <c r="F24" t="n">
-        <v>0.195</v>
+        <v>2.67</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0405</v>
+        <v>-4.9669</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>-0.5353</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0405</v>
+        <v>-4.4316</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0405</v>
+        <v>-4.6269</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>0.2262</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0405</v>
+        <v>-4.8531</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>-0.7615</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>0.4215</v>
       </c>
       <c r="P24" t="n">
-        <v>0.195</v>
+        <v>0.7799</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-1.1699</v>
       </c>
       <c r="R24" t="n">
-        <v>0.195</v>
+        <v>1.9499</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0589</v>
+        <v>0.4192</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0589</v>
+        <v>-0.641</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.0601</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2451,7 +2451,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>H. APARICIO RODRIGUEZ</t>
+          <t>H. FACORAT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2463,67 +2463,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.1267</v>
+        <v>-3.2665</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.146</v>
+        <v>-3.8098</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0194</v>
+        <v>0.5433</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.4341</v>
+        <v>-1.8699</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.4026</v>
+        <v>-3.0365</v>
       </c>
       <c r="I25" t="n">
-        <v>1.9686</v>
+        <v>1.1665</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1795</v>
+        <v>-1.3235</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.238</v>
+        <v>-2.6196</v>
       </c>
       <c r="L25" t="n">
-        <v>1.4176</v>
+        <v>1.296</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.6136</v>
+        <v>-0.5464</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.1646</v>
+        <v>-0.4169</v>
       </c>
       <c r="O25" t="n">
-        <v>0.551</v>
+        <v>-0.1295</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.195</v>
+        <v>-1.5599</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9749</v>
+        <v>-2.1448</v>
       </c>
       <c r="R25" t="n">
-        <v>0.7799</v>
+        <v>0.585</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4976</v>
+        <v>-0.1682</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3506</v>
+        <v>-0.3415</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.147</v>
+        <v>0.1733</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.3315</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>0.3315</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S. GRADIN</t>
+          <t>M. SOLA IDRISU</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2546,67 +2546,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.2701</v>
+        <v>-3.9797</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.1469</v>
+        <v>-6.1172</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8768</v>
+        <v>2.1375</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.5962</v>
+        <v>-1.8689</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6526</v>
+        <v>-0.2569</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.2488</v>
+        <v>-1.612</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.2629</v>
+        <v>-1.3239</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0496</v>
+        <v>0.0291</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.3125</v>
+        <v>-1.353</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.3333</v>
+        <v>-0.545</v>
       </c>
       <c r="N26" t="n">
-        <v>0.603</v>
+        <v>-0.286</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.9363</v>
+        <v>-0.259</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.7799</v>
+        <v>-3.5097</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.9499</v>
+        <v>-5.0696</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1699</v>
+        <v>1.5599</v>
       </c>
       <c r="S26" t="n">
-        <v>1.0531</v>
+        <v>0.5104</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1542</v>
+        <v>-0.6122</v>
       </c>
       <c r="U26" t="n">
-        <v>1.2073</v>
+        <v>1.1226</v>
       </c>
       <c r="V26" t="n">
-        <v>0.0529</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>1.2201</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.1671</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>P. ROBLES LLANOS</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2629,318 +2629,69 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.8792</v>
+        <v>-6.1256</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.5492</v>
+        <v>-15.6079</v>
       </c>
       <c r="F27" t="n">
-        <v>2.67</v>
+        <v>9.4823</v>
       </c>
       <c r="G27" t="n">
-        <v>-4.9669</v>
+        <v>-4.1089</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.5353</v>
+        <v>-4.1089</v>
       </c>
       <c r="I27" t="n">
-        <v>-4.4316</v>
+        <v>9.999999999976694e-05</v>
       </c>
       <c r="J27" t="n">
-        <v>-4.6269</v>
+        <v>-0.0378000000000005</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2262</v>
+        <v>-0.6031999999999998</v>
       </c>
       <c r="L27" t="n">
-        <v>-4.8531</v>
+        <v>0.5650999999999997</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.34</v>
+        <v>-4.071</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.7615</v>
+        <v>-3.5058</v>
       </c>
       <c r="O27" t="n">
-        <v>0.4215</v>
+        <v>-0.5652000000000001</v>
       </c>
       <c r="P27" t="n">
-        <v>0.7799</v>
+        <v>-3.8997</v>
       </c>
       <c r="Q27" t="n">
-        <v>-1.1699</v>
+        <v>-15.5988</v>
       </c>
       <c r="R27" t="n">
-        <v>1.9499</v>
+        <v>11.6991</v>
       </c>
       <c r="S27" t="n">
-        <v>0.4192</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.641</v>
+        <v>-4.971299999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>1.0601</v>
+        <v>4.971100000000001</v>
       </c>
       <c r="V27" t="n">
-        <v>0.8885999999999999</v>
+        <v>1.8829</v>
       </c>
       <c r="W27" t="n">
-        <v>0.8885999999999999</v>
+        <v>5.0001</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>play_by_play_2536137_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>H. FACORAT</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>MOVISTAR ESTUDIANTES</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="n">
-        <v>-3.2665</v>
-      </c>
-      <c r="E28" t="n">
-        <v>-3.8098</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.5433</v>
-      </c>
-      <c r="G28" t="n">
-        <v>-1.8699</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-3.0365</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1.1665</v>
-      </c>
-      <c r="J28" t="n">
-        <v>-1.3235</v>
-      </c>
-      <c r="K28" t="n">
-        <v>-2.6196</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1.296</v>
-      </c>
-      <c r="M28" t="n">
-        <v>-0.5464</v>
-      </c>
-      <c r="N28" t="n">
-        <v>-0.4169</v>
-      </c>
-      <c r="O28" t="n">
-        <v>-0.1295</v>
-      </c>
-      <c r="P28" t="n">
-        <v>-1.5599</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>-2.1448</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="S28" t="n">
-        <v>-0.1682</v>
-      </c>
-      <c r="T28" t="n">
-        <v>-0.3415</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0.1733</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0.3315</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0.3315</v>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>play_by_play_2536137_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>M. SOLA IDRISU</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>MOVISTAR ESTUDIANTES</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="n">
-        <v>-3.9797</v>
-      </c>
-      <c r="E29" t="n">
-        <v>-6.1172</v>
-      </c>
-      <c r="F29" t="n">
-        <v>2.1375</v>
-      </c>
-      <c r="G29" t="n">
-        <v>-1.8689</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-0.2569</v>
-      </c>
-      <c r="I29" t="n">
-        <v>-1.612</v>
-      </c>
-      <c r="J29" t="n">
-        <v>-1.3239</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.0291</v>
-      </c>
-      <c r="L29" t="n">
-        <v>-1.353</v>
-      </c>
-      <c r="M29" t="n">
-        <v>-0.545</v>
-      </c>
-      <c r="N29" t="n">
-        <v>-0.286</v>
-      </c>
-      <c r="O29" t="n">
-        <v>-0.259</v>
-      </c>
-      <c r="P29" t="n">
-        <v>-3.5097</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>-5.0696</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.5599</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0.5104</v>
-      </c>
-      <c r="T29" t="n">
-        <v>-0.6122</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.1226</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0.8885999999999999</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0.8885999999999999</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>play_by_play_2536137_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>MOVISTAR ESTUDIANTES</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" t="n">
-        <v>-6.1257</v>
-      </c>
-      <c r="E30" t="n">
-        <v>-15.6079</v>
-      </c>
-      <c r="F30" t="n">
-        <v>9.4823</v>
-      </c>
-      <c r="G30" t="n">
-        <v>-4.1089</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-4.1089</v>
-      </c>
-      <c r="I30" t="n">
-        <v>9.999999999887876e-05</v>
-      </c>
-      <c r="J30" t="n">
-        <v>-0.03789999999999849</v>
-      </c>
-      <c r="K30" t="n">
-        <v>-0.6031999999999996</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0.5650999999999997</v>
-      </c>
-      <c r="M30" t="n">
-        <v>-4.071</v>
-      </c>
-      <c r="N30" t="n">
-        <v>-3.5058</v>
-      </c>
-      <c r="O30" t="n">
-        <v>-0.5652000000000001</v>
-      </c>
-      <c r="P30" t="n">
-        <v>-3.8997</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>-15.5988</v>
-      </c>
-      <c r="R30" t="n">
-        <v>11.6991</v>
-      </c>
-      <c r="S30" t="n">
-        <v>-1.110223024625157e-16</v>
-      </c>
-      <c r="T30" t="n">
-        <v>-4.971299999999999</v>
-      </c>
-      <c r="U30" t="n">
-        <v>4.971100000000001</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.8829</v>
-      </c>
-      <c r="W30" t="n">
-        <v>5.0001</v>
-      </c>
-      <c r="X30" t="n">
         <v>-3.1171</v>
       </c>
-      <c r="Y30" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
